--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-type-savoir-faire-profession-pharmacien.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
